--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -12151,7 +12151,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>245</v>
       </c>
@@ -12170,7 +12170,7 @@
         <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>74</v>
@@ -12456,7 +12456,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>253</v>
       </c>
@@ -12471,13 +12471,13 @@
         <v>62</v>
       </c>
       <c r="F83" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>74</v>
@@ -12559,7 +12559,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>257</v>
       </c>
@@ -12574,13 +12574,13 @@
         <v>258</v>
       </c>
       <c r="F84" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -12868,7 +12868,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>271</v>
       </c>
@@ -12889,7 +12889,7 @@
         <v>75</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>74</v>
+        <v>239</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-prescrit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
